--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2025" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="412">
   <si>
     <t>Property</t>
   </si>
@@ -51,16 +51,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>MedicationAdministration profile for insulin administered due to hyperglycemia.</t>
+    <t>MedicationAdministration profile for insulin administered in response to hyperglycemia.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -650,7 +650,7 @@
 </t>
   </si>
   <si>
-    <t>Part of referenced event</t>
+    <t>Procedure this administration supports</t>
   </si>
   <si>
     <t>A larger event of which this particular event is a component or step.</t>
@@ -668,7 +668,7 @@
     <t>MedicationAdministration.status</t>
   </si>
   <si>
-    <t>in-progress | not-done | on-hold | completed | entered-in-error | stopped | unknown</t>
+    <t>Medication administration status</t>
   </si>
   <si>
     <t>Will generally be set to show that the administration has been completed.  For some long running administrations such as infusions, it is possible for an administration to be started but not completed or it may be paused while some other process is under way.</t>
@@ -698,7 +698,7 @@
     <t>MedicationAdministration.statusReason</t>
   </si>
   <si>
-    <t>Reason administration not performed</t>
+    <t>Reason medication was not given or status rationale</t>
   </si>
   <si>
     <t>A code indicating why the administration was not performed.</t>
@@ -747,7 +747,7 @@
 </t>
   </si>
   <si>
-    <t>What was administered</t>
+    <t>Administered medication</t>
   </si>
   <si>
     <t>Identifies the medication that was administered. This is either a link to a resource representing the details of the medication or a simple attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -827,10 +827,10 @@
 </t>
   </si>
   <si>
-    <t>Who received medication</t>
-  </si>
-  <si>
-    <t>The person or animal or group receiving the medication.</t>
+    <t>RES-Q registry patient</t>
+  </si>
+  <si>
+    <t>Patient who experienced the index stroke episode represented in this registry dataset.</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -852,10 +852,10 @@
 </t>
   </si>
   <si>
-    <t>Encounter administered as part of</t>
-  </si>
-  <si>
-    <t>The visit, admission, or other contact between patient and health care provider during which the medication administration was performed.</t>
+    <t>Index stroke encounter</t>
+  </si>
+  <si>
+    <t>Encounter that anchors the clinical fact to the acute stroke episode and hospital pathway.</t>
   </si>
   <si>
     <t>Event.encounter</t>
@@ -893,7 +893,7 @@
 </t>
   </si>
   <si>
-    <t>Specific date/time or interval of time during which the administration took place (or did not take place)</t>
+    <t>Administration date/time</t>
   </si>
   <si>
     <t>A specific date/time or interval of time during which the administration took place (or did not take place). For many administrations, such as swallowing a tablet the use of dateTime is more appropriate.</t>
@@ -1050,7 +1050,7 @@
 </t>
   </si>
   <si>
-    <t>Concept, condition or observation that supports why the medication was administered</t>
+    <t>Reason or clinical trigger for administration</t>
   </si>
   <si>
     <t>A code, Condition or observation that supports why the medication was administered.</t>
@@ -1137,7 +1137,7 @@
     <t>MedicationAdministration.dosage</t>
   </si>
   <si>
-    <t>Details of how medication was taken</t>
+    <t>Dose details</t>
   </si>
   <si>
     <t>Describes the medication dosage information details e.g. dose, rate, site, route, etc.</t>
@@ -1514,98 +1514,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -1791,10 +1793,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1874,7 +1876,7 @@
         <v>77</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>78</v>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="413">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -889,29 +889,33 @@
     <t>MedicationAdministration.occurence[x]</t>
   </si>
   <si>
+    <t>dateTime
+Period</t>
+  </si>
+  <si>
+    <t>Administration date/time</t>
+  </si>
+  <si>
+    <t>A specific date/time or interval of time during which the administration took place (or did not take place). For many administrations, such as swallowing a tablet the use of dateTime is more appropriate.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>RXA-3 Date/Time Start of Administration / RXA-4 Date/Time End of Administration</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.recorded</t>
+  </si>
+  <si>
     <t xml:space="preserve">dateTime
 </t>
-  </si>
-  <si>
-    <t>Administration date/time</t>
-  </si>
-  <si>
-    <t>A specific date/time or interval of time during which the administration took place (or did not take place). For many administrations, such as swallowing a tablet the use of dateTime is more appropriate.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>RXA-3 Date/Time Start of Administration / RXA-4 Date/Time End of Administration</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.recorded</t>
   </si>
   <si>
     <t>When the MedicationAdministration was first captured in the subject's record</t>
@@ -5315,13 +5319,13 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5390,10 +5394,10 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5401,10 +5405,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5427,13 +5431,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5484,7 +5488,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5513,10 +5517,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5542,10 +5546,10 @@
         <v>174</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5576,7 +5580,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5594,7 +5598,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5623,10 +5627,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5649,13 +5653,13 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5706,7 +5710,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5721,24 +5725,24 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5761,7 +5765,7 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>156</v>
@@ -5847,10 +5851,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5961,14 +5965,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5990,10 +5994,10 @@
         <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>184</v>
@@ -6048,7 +6052,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6077,10 +6081,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6106,10 +6110,10 @@
         <v>174</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6139,10 +6143,10 @@
         <v>228</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -6160,7 +6164,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6175,13 +6179,13 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6189,10 +6193,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6215,13 +6219,13 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6272,7 +6276,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>88</v>
@@ -6287,13 +6291,13 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6301,10 +6305,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6327,13 +6331,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6363,10 +6367,10 @@
         <v>228</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
@@ -6384,7 +6388,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6399,24 +6403,24 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6439,16 +6443,16 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6498,7 +6502,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6513,24 +6517,24 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6553,13 +6557,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6610,7 +6614,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6631,18 +6635,18 @@
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6665,13 +6669,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6722,7 +6726,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6737,13 +6741,13 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6751,10 +6755,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6777,13 +6781,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6834,7 +6838,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6846,7 +6850,7 @@
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -6855,7 +6859,7 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -6863,10 +6867,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6889,7 +6893,7 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>156</v>
@@ -6975,10 +6979,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7089,14 +7093,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7118,10 +7122,10 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>184</v>
@@ -7176,7 +7180,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7205,10 +7209,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7231,13 +7235,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7288,7 +7292,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7297,7 +7301,7 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
@@ -7309,7 +7313,7 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7317,10 +7321,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7346,13 +7350,13 @@
         <v>174</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7381,10 +7385,10 @@
         <v>228</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7402,7 +7406,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7423,18 +7427,18 @@
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7460,10 +7464,10 @@
         <v>174</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7493,10 +7497,10 @@
         <v>228</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -7514,7 +7518,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7535,18 +7539,18 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7572,13 +7576,13 @@
         <v>174</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7607,10 +7611,10 @@
         <v>228</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -7628,7 +7632,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7649,18 +7653,18 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7683,16 +7687,16 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7742,7 +7746,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7751,7 +7755,7 @@
         <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>100</v>
@@ -7763,18 +7767,18 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7797,16 +7801,16 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7856,7 +7860,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7865,7 +7869,7 @@
         <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>100</v>
@@ -7877,18 +7881,18 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7911,16 +7915,16 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7970,7 +7974,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7991,7 +7995,7 @@
         <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$55</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="411">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -492,13 +492,7 @@
     <t>Timing category used by medication-administration builders, e.g. insulin within one hour or paracetamol timing. The Python code contains a typo variant tecnomod-um-org; this IG normalizes to tecnomod-um.org.</t>
   </si>
   <si>
-    <t>MedicationAdministration.extension:insulinTiming</t>
-  </si>
-  <si>
-    <t>insulinTiming</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.extension:insulinTiming.id</t>
+    <t>MedicationAdministration.extension:assessmentTiming.id</t>
   </si>
   <si>
     <t>MedicationAdministration.extension.id</t>
@@ -520,7 +514,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationAdministration.extension:insulinTiming.extension</t>
+    <t>MedicationAdministration.extension:assessmentTiming.extension</t>
   </si>
   <si>
     <t>MedicationAdministration.extension.extension</t>
@@ -532,7 +526,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationAdministration.extension:insulinTiming.url</t>
+    <t>MedicationAdministration.extension:assessmentTiming.url</t>
   </si>
   <si>
     <t>MedicationAdministration.extension.url</t>
@@ -553,7 +547,7 @@
     <t>Extension.url</t>
   </si>
   <si>
-    <t>MedicationAdministration.extension:insulinTiming.value[x]</t>
+    <t>MedicationAdministration.extension:assessmentTiming.value[x]</t>
   </si>
   <si>
     <t>MedicationAdministration.extension.value[x]</t>
@@ -1629,10 +1623,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN56"/>
+  <dimension ref="A1:AN55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.40234375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.6015625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.1796875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="19.0859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2927,16 +2921,14 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C12" t="s" s="2">
         <v>153</v>
       </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>77</v>
       </c>
@@ -2948,7 +2940,7 @@
         <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>77</v>
@@ -2957,13 +2949,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3014,19 +3006,19 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>77</v>
@@ -3035,7 +3027,7 @@
         <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -3043,10 +3035,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3057,7 +3049,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
@@ -3069,13 +3061,13 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3114,31 +3106,31 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
@@ -3147,7 +3139,7 @@
         <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -3155,10 +3147,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3166,10 +3158,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
@@ -3181,22 +3173,24 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>77</v>
@@ -3226,31 +3220,31 @@
         <v>77</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>163</v>
+        <v>77</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -3259,18 +3253,18 @@
         <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3284,7 +3278,7 @@
         <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>77</v>
@@ -3293,24 +3287,22 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>102</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="S15" t="s" s="2">
         <v>77</v>
@@ -3328,13 +3320,11 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3352,19 +3342,19 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
@@ -3379,44 +3369,48 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I16" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I16" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="J16" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
       </c>
@@ -3440,11 +3434,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3462,19 +3458,19 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
@@ -3491,14 +3487,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3511,26 +3507,24 @@
         <v>77</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
       </c>
@@ -3578,7 +3572,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3590,16 +3584,16 @@
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3607,10 +3601,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3633,17 +3627,15 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3692,7 +3684,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3707,24 +3699,24 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3738,24 +3730,26 @@
         <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3804,7 +3798,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3819,13 +3813,13 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -3833,10 +3827,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3844,31 +3838,31 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>89</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>108</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3894,13 +3888,13 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>77</v>
@@ -3918,13 +3912,13 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
@@ -3933,24 +3927,24 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3958,32 +3952,30 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>89</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>172</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -4008,13 +4000,11 @@
         <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>77</v>
@@ -4032,13 +4022,13 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
@@ -4047,24 +4037,24 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4078,7 +4068,7 @@
         <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>77</v>
@@ -4087,13 +4077,13 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4120,11 +4110,13 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
@@ -4142,7 +4134,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4157,24 +4149,24 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>224</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4182,30 +4174,32 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>174</v>
+        <v>231</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4230,37 +4224,35 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AA23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>225</v>
-      </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
@@ -4269,24 +4261,24 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>77</v>
+        <v>237</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>77</v>
+        <v>239</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4294,32 +4286,30 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>233</v>
+        <v>90</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4344,11 +4334,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>237</v>
+        <v>77</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4366,50 +4358,50 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>156</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>238</v>
+        <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>239</v>
+        <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>240</v>
+        <v>158</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>241</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4421,15 +4413,17 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>156</v>
+        <v>242</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4466,40 +4460,40 @@
         <v>77</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF25" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4507,21 +4501,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4530,20 +4524,18 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4553,7 +4545,7 @@
         <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>77</v>
@@ -4580,31 +4572,31 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>163</v>
+        <v>77</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>164</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
@@ -4613,7 +4605,7 @@
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4621,10 +4613,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4647,13 +4639,13 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>174</v>
+        <v>250</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4665,7 +4657,7 @@
         <v>77</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>249</v>
+        <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>77</v>
@@ -4704,7 +4696,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4731,12 +4723,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4744,13 +4736,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>77</v>
@@ -4759,13 +4751,13 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4816,10 +4808,10 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>88</v>
@@ -4831,24 +4823,24 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>77</v>
+        <v>258</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>77</v>
+        <v>259</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>77</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4868,16 +4860,16 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4928,10 +4920,10 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>88</v>
@@ -4943,24 +4935,24 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4968,13 +4960,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>77</v>
@@ -4983,13 +4975,13 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5040,13 +5032,13 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
@@ -5055,24 +5047,24 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>268</v>
+        <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>271</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5080,28 +5072,28 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5152,13 +5144,13 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
@@ -5167,24 +5159,24 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>77</v>
+        <v>279</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5192,13 +5184,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>77</v>
@@ -5207,13 +5199,13 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5264,10 +5256,10 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>88</v>
@@ -5279,24 +5271,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>284</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5316,16 +5308,16 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5376,7 +5368,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5394,10 +5386,10 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>289</v>
+        <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5405,10 +5397,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5419,7 +5411,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5431,13 +5423,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>292</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5464,13 +5456,11 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>77</v>
+        <v>296</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5488,13 +5478,13 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
@@ -5517,10 +5507,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5540,16 +5530,16 @@
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>174</v>
+        <v>298</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5576,11 +5566,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5598,7 +5590,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5613,24 +5605,24 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>77</v>
+        <v>301</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>77</v>
+        <v>302</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>77</v>
+        <v>303</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>77</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5641,7 +5633,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -5650,16 +5642,16 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>154</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
+        <v>155</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5710,31 +5702,31 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>299</v>
+        <v>156</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>305</v>
+        <v>158</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>306</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -5746,14 +5738,14 @@
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
@@ -5765,15 +5757,17 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>308</v>
+        <v>135</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>156</v>
+        <v>242</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5822,28 +5816,28 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -5851,14 +5845,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>181</v>
+        <v>309</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5871,24 +5865,26 @@
         <v>77</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>244</v>
+        <v>310</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>245</v>
+        <v>311</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
       </c>
@@ -5936,7 +5932,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>164</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5957,7 +5953,7 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -5965,46 +5961,42 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>311</v>
+        <v>77</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -6028,13 +6020,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>77</v>
+        <v>316</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>77</v>
+        <v>317</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -6052,28 +6044,28 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>77</v>
+        <v>318</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>133</v>
+        <v>319</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6081,10 +6073,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6092,7 +6084,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>88</v>
@@ -6104,16 +6096,16 @@
         <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>174</v>
+        <v>321</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6140,13 +6132,13 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>318</v>
+        <v>77</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>319</v>
+        <v>77</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -6164,10 +6156,10 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>88</v>
@@ -6179,24 +6171,24 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6207,25 +6199,25 @@
         <v>88</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6252,13 +6244,13 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>77</v>
+        <v>330</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>77</v>
+        <v>331</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -6276,13 +6268,13 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
@@ -6291,24 +6283,24 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>77</v>
+        <v>334</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6316,13 +6308,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G42" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H42" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>77</v>
@@ -6331,15 +6323,17 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6364,13 +6358,13 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>332</v>
+        <v>77</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>333</v>
+        <v>77</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
@@ -6388,13 +6382,13 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
@@ -6403,24 +6397,24 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6431,7 +6425,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6443,17 +6437,15 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6502,13 +6494,13 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
@@ -6517,24 +6509,24 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>342</v>
+        <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6557,13 +6549,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6614,7 +6606,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6629,24 +6621,24 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>77</v>
+        <v>353</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>350</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6657,10 +6649,10 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>77</v>
@@ -6669,13 +6661,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>352</v>
+        <v>298</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6726,39 +6718,39 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>358</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>355</v>
+        <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6772,7 +6764,7 @@
         <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>77</v>
@@ -6781,13 +6773,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>358</v>
+        <v>154</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>359</v>
+        <v>155</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6838,7 +6830,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>357</v>
+        <v>156</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6847,10 +6839,10 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -6859,7 +6851,7 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>361</v>
+        <v>158</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -6867,21 +6859,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6893,15 +6885,17 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>308</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>156</v>
+        <v>242</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -6950,28 +6944,28 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -6979,14 +6973,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>181</v>
+        <v>309</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6999,24 +6993,26 @@
         <v>77</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>244</v>
+        <v>310</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>245</v>
+        <v>311</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
       </c>
@@ -7064,7 +7060,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>164</v>
+        <v>312</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7085,7 +7081,7 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7093,46 +7089,42 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>311</v>
+        <v>77</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>306</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>312</v>
+        <v>364</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7180,19 +7172,19 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>314</v>
+        <v>363</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>366</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7201,7 +7193,7 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>133</v>
+        <v>367</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7209,10 +7201,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7235,15 +7227,17 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>308</v>
+        <v>172</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7268,13 +7262,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>77</v>
+        <v>372</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>77</v>
+        <v>373</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7292,7 +7286,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7301,7 +7295,7 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
@@ -7313,18 +7307,18 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>77</v>
+        <v>375</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7347,17 +7341,15 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7382,13 +7374,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7406,7 +7398,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7427,18 +7419,18 @@
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7461,15 +7453,17 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7494,13 +7488,13 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -7518,7 +7512,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7539,18 +7533,18 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7564,7 +7558,7 @@
         <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>77</v>
@@ -7573,16 +7567,16 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>174</v>
+        <v>392</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7608,13 +7602,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>390</v>
+        <v>77</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -7632,7 +7626,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7641,7 +7635,7 @@
         <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>77</v>
+        <v>366</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>100</v>
@@ -7653,18 +7647,18 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7678,7 +7672,7 @@
         <v>88</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>77</v>
@@ -7687,16 +7681,16 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7746,7 +7740,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7755,7 +7749,7 @@
         <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>100</v>
@@ -7767,18 +7761,18 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7789,7 +7783,7 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -7801,16 +7795,16 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7860,16 +7854,16 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>100</v>
@@ -7881,128 +7875,14 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AN56" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN56">
+  <autoFilter ref="A1:AN55">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8012,7 +7892,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI55">
+  <conditionalFormatting sqref="A2:AI54">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-insulin-on-hyperglycemia-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
